--- a/tests/test_respaldo.xlsx
+++ b/tests/test_respaldo.xlsx
@@ -536,7 +536,7 @@
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-11T20:29:06.960Z</t>
+          <t xml:space="preserve">2026-10-11T21:18:25.099Z</t>
         </is>
       </c>
     </row>
